--- a/testdata/realdata/boards.xlsx
+++ b/testdata/realdata/boards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>板卡类型</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +538,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +570,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +602,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +634,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +666,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +698,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +730,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +762,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +794,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +826,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +858,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +890,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +922,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -874,6 +954,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -901,6 +986,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +1018,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1050,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1082,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,6 +1114,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1036,6 +1146,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1063,6 +1178,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1090,6 +1210,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1117,6 +1242,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1144,6 +1274,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1171,6 +1306,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1198,6 +1338,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1225,6 +1370,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1252,6 +1402,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1279,6 +1434,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1466,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1333,6 +1498,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1360,6 +1530,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1387,6 +1562,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1414,6 +1594,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1441,6 +1626,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1468,6 +1658,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1495,6 +1690,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1522,6 +1722,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1549,6 +1754,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1576,6 +1786,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1603,6 +1818,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1630,6 +1850,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1657,6 +1882,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1684,6 +1914,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1711,6 +1946,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1738,6 +1978,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1765,6 +2010,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1792,6 +2042,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1819,6 +2074,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1846,6 +2106,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1873,6 +2138,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1900,6 +2170,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1927,6 +2202,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1954,6 +2234,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1981,6 +2266,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2008,6 +2298,11 @@
           <t>主控板</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2035,6 +2330,11 @@
           <t>线路板</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2060,6 +2360,11 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>主控板</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/boards.xlsx
+++ b/testdata/realdata/boards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRD-DEV-279116876-01-01</t>
+          <t>BRD-DEV-1603990225-01-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEV-279116876-01</t>
+          <t>DEV-1603990225-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRD-DEV-279116876-01-02</t>
+          <t>BRD-DEV-1603990225-01-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEV-279116876-01</t>
+          <t>DEV-1603990225-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRD-DEV-279116876-02-01</t>
+          <t>BRD-DEV-1603990225-02-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEV-279116876-02</t>
+          <t>DEV-1603990225-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,12 +547,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRD-DEV-279116876-02-02</t>
+          <t>BRD-DEV-1603990225-02-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEV-279116876-02</t>
+          <t>DEV-1603990225-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRD-DEV-244077958-01-01</t>
+          <t>BRD-DEV-1727803072-01-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEV-244077958-01</t>
+          <t>DEV-1727803072-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRD-DEV-244077958-01-02</t>
+          <t>BRD-DEV-1727803072-01-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEV-244077958-01</t>
+          <t>DEV-1727803072-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRD-DEV-244077958-02-01</t>
+          <t>BRD-DEV-1933473774-01-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEV-244077958-02</t>
+          <t>DEV-1933473774-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRD-DEV-244077958-02-02</t>
+          <t>BRD-DEV-1933473774-01-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEV-244077958-02</t>
+          <t>DEV-1933473774-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -707,12 +707,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081515-01-01</t>
+          <t>BRD-DEV-1933473774-02-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEV-244081515-01</t>
+          <t>DEV-1933473774-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -739,12 +739,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081515-01-02</t>
+          <t>BRD-DEV-1933473774-02-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEV-244081515-01</t>
+          <t>DEV-1933473774-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081515-02-01</t>
+          <t>BRD-DEV-1933473774-03-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEV-244081515-02</t>
+          <t>DEV-1933473774-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081515-02-02</t>
+          <t>BRD-DEV-1933473774-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEV-244081515-02</t>
+          <t>DEV-1933473774-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -835,12 +835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRD-DEV-1727803072-01-01</t>
+          <t>BRD-DEV-2168737545-01-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEV-1727803072-01</t>
+          <t>DEV-2168737545-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRD-DEV-1727803072-01-02</t>
+          <t>BRD-DEV-2168737545-01-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEV-1727803072-01</t>
+          <t>DEV-2168737545-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRD-DEV-1727803072-02-01</t>
+          <t>BRD-DEV-2168737545-02-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEV-1727803072-02</t>
+          <t>DEV-2168737545-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRD-DEV-1727803072-02-02</t>
+          <t>BRD-DEV-2168737545-02-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEV-1727803072-02</t>
+          <t>DEV-2168737545-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRD-DEV-469656125-01-01</t>
+          <t>BRD-DEV-2289935762-01-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEV-469656125-01</t>
+          <t>DEV-2289935762-01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -995,12 +995,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BRD-DEV-469656125-01-02</t>
+          <t>BRD-DEV-2289935762-01-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEV-469656125-01</t>
+          <t>DEV-2289935762-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BRD-DEV-469656125-02-01</t>
+          <t>BRD-DEV-244076868-01-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEV-469656125-02</t>
+          <t>DEV-244076868-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1059,12 +1059,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BRD-DEV-469656125-02-02</t>
+          <t>BRD-DEV-244076868-01-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEV-469656125-02</t>
+          <t>DEV-244076868-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRD-DEV-678337697-01-01</t>
+          <t>BRD-DEV-244076933-01-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEV-678337697-01</t>
+          <t>DEV-244076933-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRD-DEV-678337697-01-02</t>
+          <t>BRD-DEV-244076933-01-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEV-678337697-01</t>
+          <t>DEV-244076933-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1155,12 +1155,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BRD-DEV-678337697-02-01</t>
+          <t>BRD-DEV-244076933-02-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEV-678337697-02</t>
+          <t>DEV-244076933-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRD-DEV-678337697-02-02</t>
+          <t>BRD-DEV-244076933-02-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEV-678337697-02</t>
+          <t>DEV-244076933-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BRD-DEV-962010355-01-01</t>
+          <t>BRD-DEV-244077958-01-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DEV-962010355-01</t>
+          <t>DEV-244077958-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRD-DEV-962010355-01-02</t>
+          <t>BRD-DEV-244077958-01-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEV-962010355-01</t>
+          <t>DEV-244077958-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRD-DEV-962010355-02-01</t>
+          <t>BRD-DEV-244077958-02-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DEV-962010355-02</t>
+          <t>DEV-244077958-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRD-DEV-962010355-02-02</t>
+          <t>BRD-DEV-244077958-02-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DEV-962010355-02</t>
+          <t>DEV-244077958-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRD-DEV-280162986-01-01</t>
+          <t>BRD-DEV-244077958-03-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DEV-280162986-01</t>
+          <t>DEV-244077958-03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1379,12 +1379,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BRD-DEV-280162986-01-02</t>
+          <t>BRD-DEV-244077958-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DEV-280162986-01</t>
+          <t>DEV-244077958-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1411,12 +1411,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BRD-DEV-280162986-02-01</t>
+          <t>BRD-DEV-244079035-01-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DEV-280162986-02</t>
+          <t>DEV-244079035-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1443,12 +1443,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BRD-DEV-280162986-02-02</t>
+          <t>BRD-DEV-244079035-01-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DEV-280162986-02</t>
+          <t>DEV-244079035-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1475,12 +1475,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRD-DEV-4059698545-01-01</t>
+          <t>BRD-DEV-244079624-01-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DEV-4059698545-01</t>
+          <t>DEV-244079624-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BRD-DEV-4059698545-01-02</t>
+          <t>BRD-DEV-244079624-01-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DEV-4059698545-01</t>
+          <t>DEV-244079624-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1539,12 +1539,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BRD-DEV-4059698545-02-01</t>
+          <t>BRD-DEV-244079624-02-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DEV-4059698545-02</t>
+          <t>DEV-244079624-02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1571,12 +1571,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BRD-DEV-4059698545-02-02</t>
+          <t>BRD-DEV-244079624-02-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DEV-4059698545-02</t>
+          <t>DEV-244079624-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BRD-DEV-304758391-01-01</t>
+          <t>BRD-DEV-244080476-01-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DEV-304758391-01</t>
+          <t>DEV-244080476-01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BRD-DEV-304758391-01-02</t>
+          <t>BRD-DEV-244080476-01-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DEV-304758391-01</t>
+          <t>DEV-244080476-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1660,19 +1660,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>在网</t>
+          <t>停用</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRD-DEV-304758391-02-01</t>
+          <t>BRD-DEV-244080476-02-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DEV-304758391-02</t>
+          <t>DEV-244080476-02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BRD-DEV-304758391-02-02</t>
+          <t>BRD-DEV-244080476-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DEV-304758391-02</t>
+          <t>DEV-244080476-02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1724,19 +1724,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>在网</t>
+          <t>停用</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BRD-DEV-6359892789-01-01</t>
+          <t>BRD-DEV-244080476-03-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DEV-6359892789-01</t>
+          <t>DEV-244080476-03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BRD-DEV-6359892789-01-02</t>
+          <t>BRD-DEV-244080476-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DEV-6359892789-01</t>
+          <t>DEV-244080476-03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRD-DEV-6359892789-02-01</t>
+          <t>BRD-DEV-244080682-01-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DEV-6359892789-02</t>
+          <t>DEV-244080682-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1827,12 +1827,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BRD-DEV-6359892789-02-02</t>
+          <t>BRD-DEV-244080682-01-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEV-6359892789-02</t>
+          <t>DEV-244080682-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>停用</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081815-01-01</t>
+          <t>BRD-DEV-244080693-01-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEV-244081815-01</t>
+          <t>DEV-244080693-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081815-01-02</t>
+          <t>BRD-DEV-244080693-01-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DEV-244081815-01</t>
+          <t>DEV-244080693-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081815-02-01</t>
+          <t>BRD-DEV-244080693-02-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DEV-244081815-02</t>
+          <t>DEV-244080693-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1955,12 +1955,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081815-02-02</t>
+          <t>BRD-DEV-244080693-02-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DEV-244081815-02</t>
+          <t>DEV-244080693-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BRD-DEV-244082251-01-01</t>
+          <t>BRD-DEV-244081168-01-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DEV-244082251-01</t>
+          <t>DEV-244081168-01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BRD-DEV-244082251-01-02</t>
+          <t>BRD-DEV-244081168-01-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DEV-244082251-01</t>
+          <t>DEV-244081168-01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BRD-DEV-244082251-02-01</t>
+          <t>BRD-DEV-244081218-01-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DEV-244082251-02</t>
+          <t>DEV-244081218-01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BRD-DEV-244082251-02-02</t>
+          <t>BRD-DEV-244081218-01-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DEV-244082251-02</t>
+          <t>DEV-244081218-01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2115,12 +2115,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081526-01-01</t>
+          <t>BRD-DEV-244081226-01-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DEV-244081526-01</t>
+          <t>DEV-244081226-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081526-01-02</t>
+          <t>BRD-DEV-244081226-01-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DEV-244081526-01</t>
+          <t>DEV-244081226-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2179,12 +2179,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081526-02-01</t>
+          <t>BRD-DEV-244081226-02-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DEV-244081526-02</t>
+          <t>DEV-244081226-02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2211,12 +2211,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BRD-DEV-244081526-02-02</t>
+          <t>BRD-DEV-244081226-02-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DEV-244081526-02</t>
+          <t>DEV-244081226-02</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BRD-DEV-502220401-01-01</t>
+          <t>BRD-DEV-244081487-01-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DEV-502220401-01</t>
+          <t>DEV-244081487-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2275,12 +2275,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BRD-DEV-502220401-01-02</t>
+          <t>BRD-DEV-244081487-01-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DEV-502220401-01</t>
+          <t>DEV-244081487-01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2307,12 +2307,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BRD-DEV-502220401-02-01</t>
+          <t>BRD-DEV-244081508-01-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DEV-502220401-02</t>
+          <t>DEV-244081508-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2339,30 +2339,6622 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>BRD-DEV-244081508-01-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DEV-244081508-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DEV-244081515-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-01-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>DEV-244081515-01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-02-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DEV-244081515-02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-02-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>DEV-244081515-02</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-03-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DEV-244081515-03</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-03-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DEV-244081515-03</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-01-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DEV-244081526-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-01-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>DEV-244081526-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-02-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DEV-244081526-02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-02-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DEV-244081526-02</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-03-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DEV-244081526-03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-03-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DEV-244081526-03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081804-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>DEV-244081804-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081804-01-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>DEV-244081804-01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-01-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DEV-244081815-01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-01-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DEV-244081815-01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-02-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>DEV-244081815-02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-02-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>DEV-244081815-02</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-03-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DEV-244081815-03</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-03-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>DEV-244081815-03</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081820-01-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DEV-244081820-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081820-01-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DEV-244081820-01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081838-01-01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DEV-244081838-01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081838-01-02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DEV-244081838-01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081998-01-01</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DEV-244081998-01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081998-01-02</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DEV-244081998-01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081998-02-01</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DEV-244081998-02</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081998-02-02</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>DEV-244081998-02</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082051-01-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DEV-244082051-01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082051-01-02</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DEV-244082051-01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-01-01</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DEV-244082251-01</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-01-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DEV-244082251-01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-02-01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DEV-244082251-02</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-02-02</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>DEV-244082251-02</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-03-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DEV-244082251-03</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-03-02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DEV-244082251-03</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082264-01-01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DEV-244082264-01</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082264-01-02</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DEV-244082264-01</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082264-02-01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DEV-244082264-02</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082264-02-02</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DEV-244082264-02</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082302-01-01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DEV-244082302-01</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082302-01-02</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DEV-244082302-01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083414-01-01</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DEV-244083414-01</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083414-01-02</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DEV-244083414-01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083759-01-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DEV-244083759-01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083759-01-02</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>DEV-244083759-01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083759-02-01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DEV-244083759-02</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083759-02-02</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DEV-244083759-02</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083846-01-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>DEV-244083846-01</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244083846-01-02</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DEV-244083846-01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084005-01-01</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>DEV-244084005-01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084005-01-02</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>DEV-244084005-01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084006-01-01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>DEV-244084006-01</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084006-01-02</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>DEV-244084006-01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084006-02-01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DEV-244084006-02</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084006-02-02</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DEV-244084006-02</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084008-01-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DEV-244084008-01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084008-01-02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>DEV-244084008-01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084009-01-01</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>DEV-244084009-01</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084009-01-02</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>DEV-244084009-01</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084010-01-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>DEV-244084010-01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084010-01-02</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>DEV-244084010-01</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084010-02-01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>DEV-244084010-02</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084010-02-02</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>DEV-244084010-02</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084021-01-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>DEV-244084021-01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084021-01-02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>DEV-244084021-01</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084024-01-01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DEV-244084024-01</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084024-01-02</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>DEV-244084024-01</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084032-01-01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DEV-244084032-01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084032-01-02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DEV-244084032-01</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084032-02-01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DEV-244084032-02</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084032-02-02</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DEV-244084032-02</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084349-01-01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DEV-244084349-01</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084349-01-02</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DEV-244084349-01</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084365-01-01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DEV-244084365-01</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244084365-01-02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DEV-244084365-01</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-01-01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DEV-279116876-01</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-01-02</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DEV-279116876-01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-02-01</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>DEV-279116876-02</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-02-02</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DEV-279116876-02</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-03-01</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DEV-279116876-03</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-03-02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DEV-279116876-03</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-01-01</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DEV-280162986-01</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-01-02</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>DEV-280162986-01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-01-01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DEV-304758391-01</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-01-02</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DEV-304758391-01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-02-01</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DEV-304758391-02</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-02-02</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>DEV-304758391-02</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-03-01</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>DEV-304758391-03</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-03-02</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DEV-304758391-03</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3364291968-01-01</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-01</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3364291968-01-02</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3364291968-02-01</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-02</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3364291968-02-02</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-02</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3373092558-01-01</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>DEV-3373092558-01</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3373092558-01-02</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>DEV-3373092558-01</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3373116121-01-01</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>DEV-3373116121-01</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3373116121-01-02</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>DEV-3373116121-01</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3768594801-01-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-01</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3768594801-01-02</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-01</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3768594801-02-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-02</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3768594801-02-02</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-02</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826287683-01-01</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DEV-3826287683-01</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826287683-01-02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>DEV-3826287683-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497558-01-01</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>DEV-3826497558-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497558-01-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DEV-3826497558-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497583-01-01</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497583-01-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497583-02-01</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-02</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BRD-DEV-3826497583-02-02</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-02</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-01-01</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-01-02</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-02-01</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-02</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-02-02</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-02</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-03-01</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-03</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-03-02</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-03</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>BRD-DEV-412234770-01-01</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DEV-412234770-01</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BRD-DEV-412234770-01-02</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>DEV-412234770-01</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4417654189-01-01</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-01</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4417654189-01-02</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-01</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4417654189-02-01</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-02</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4417654189-02-02</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-02</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-01-01</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>DEV-469656125-01</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-01-02</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>DEV-469656125-01</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-01-01</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>DEV-502220401-01</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-01-02</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>DEV-502220401-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-02-01</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>DEV-502220401-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
           <t>BRD-DEV-502220401-02-02</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>DEV-502220401-02</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>主控处理板</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>主控板</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-03-01</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>DEV-502220401-03</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-03-02</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>DEV-502220401-03</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5329377920-01-01</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-01</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5329377920-01-02</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-01</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5329377920-02-01</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-02</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5329377920-02-02</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-02</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-01-01</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-01</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-01-02</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-02-01</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-02-02</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-02</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-03-01</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-03</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BRD-DEV-5617724009-03-02</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-03</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6330273967-01-01</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>DEV-6330273967-01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6330273967-01-02</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DEV-6330273967-01</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6331568977-01-01</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-01</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6331568977-01-02</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-01</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6331568977-02-01</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-02</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6331568977-02-02</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-02</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6332406998-01-01</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DEV-6332406998-01</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6332406998-01-02</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>DEV-6332406998-01</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6341507561-01-01</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>DEV-6341507561-01</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6341507561-01-02</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DEV-6341507561-01</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6343642415-01-01</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-01</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6343642415-01-02</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-01</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6343642415-02-01</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-02</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6343642415-02-02</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-02</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6350394662-01-01</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DEV-6350394662-01</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6350394662-01-02</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>DEV-6350394662-01</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352034081-01-01</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>DEV-6352034081-01</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352034081-01-02</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>DEV-6352034081-01</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352421319-01-01</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-01</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352421319-01-02</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-01</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352421319-02-01</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-02</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6352421319-02-02</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-02</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6353763804-01-01</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>DEV-6353763804-01</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6353763804-01-02</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>DEV-6353763804-01</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6355869234-01-01</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>DEV-6355869234-01</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6355869234-01-02</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DEV-6355869234-01</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6356225091-01-01</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-01</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6356225091-01-02</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-01</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6356225091-02-01</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-02</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6356225091-02-02</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-02</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6358882012-01-01</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DEV-6358882012-01</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6358882012-01-02</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>DEV-6358882012-01</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-01-01</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>DEV-6359892789-01</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-01-02</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DEV-6359892789-01</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6373436326-01-01</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-01</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6373436326-01-02</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-01</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6373436326-02-01</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-02</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6373436326-02-02</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-02</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6375398861-01-01</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DEV-6375398861-01</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6375398861-01-02</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DEV-6375398861-01</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6375764149-01-01</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>DEV-6375764149-01</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6375764149-01-02</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DEV-6375764149-01</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6376504260-01-01</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-01</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6376504260-01-02</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-01</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6376504260-02-01</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-02</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6376504260-02-02</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-02</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6377319195-01-01</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DEV-6377319195-01</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6377319195-01-02</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DEV-6377319195-01</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380056508-01-01</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>DEV-6380056508-01</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380056508-01-02</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DEV-6380056508-01</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380925564-01-01</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-01</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380925564-01-02</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-01</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380925564-02-01</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-02</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6380925564-02-02</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-02</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6385641267-01-01</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>DEV-6385641267-01</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6385641267-01-02</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DEV-6385641267-01</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6395573965-01-01</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DEV-6395573965-01</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6395573965-01-02</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DEV-6395573965-01</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-01-01</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>DEV-678337697-01</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-01-02</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DEV-678337697-01</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-02-01</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DEV-678337697-02</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-02-02</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DEV-678337697-02</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-03-01</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DEV-678337697-03</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-03-02</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DEV-678337697-03</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-01-01</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DEV-962010355-01</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>100GE 线路板</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>线路板</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-01-02</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DEV-962010355-01</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>主控处理板</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>主控板</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
         <is>
           <t>在网</t>
         </is>
